--- a/tables/table-1-partial-fine-tuning-architecture-specifications.xlsx
+++ b/tables/table-1-partial-fine-tuning-architecture-specifications.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0574198c81a0fd8/ERP/moth-classification-research-project/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="8_{BC1D83D8-9A1B-41C5-9595-46EA070E462D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96F312B6-42F6-4C24-B0D3-6B1080D6394B}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="8_{BC1D83D8-9A1B-41C5-9595-46EA070E462D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FAFB4D2C-92C4-493B-9261-8456DB8CA34A}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{02F10342-5E92-4A97-AD09-854D91C2ECB0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{02F10342-5E92-4A97-AD09-854D91C2ECB0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
   <si>
     <t>Architecture</t>
   </si>
@@ -39,9 +39,6 @@
     <t>Trainable Parameters</t>
   </si>
   <si>
-    <t>Input Size (px)</t>
-  </si>
-  <si>
     <t>VGG16</t>
   </si>
   <si>
@@ -54,9 +51,6 @@
     <t>17.0M</t>
   </si>
   <si>
-    <t>224x224x3</t>
-  </si>
-  <si>
     <t>InceptionV3</t>
   </si>
   <si>
@@ -67,9 +61,6 @@
   </si>
   <si>
     <t>1.8M</t>
-  </si>
-  <si>
-    <t>229x229x3</t>
   </si>
   <si>
     <t>ResNet50</t>
@@ -284,9 +275,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -324,7 +315,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -430,7 +421,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -572,7 +563,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -580,27 +571,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BB5FD47-8783-4593-BDAE-5690A81077EC}">
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.453125" customWidth="1"/>
-    <col min="2" max="2" width="10.7265625" customWidth="1"/>
-    <col min="3" max="3" width="18.81640625" customWidth="1"/>
-    <col min="4" max="4" width="10.7265625" customWidth="1"/>
-    <col min="5" max="5" width="13.54296875" customWidth="1"/>
+    <col min="1" max="1" width="15.42578125" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18.85546875" customWidth="1"/>
+    <col min="4" max="4" width="10.7109375" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
       <c r="D1" s="12"/>
       <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-    </row>
-    <row r="2" spans="1:6" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:5" ht="39" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
@@ -614,155 +604,131 @@
         <v>3</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="F2" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="26" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="E3" s="10">
         <v>12.6</v>
       </c>
-      <c r="F3" s="1" t="s">
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="26" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
+      <c r="C4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>13</v>
       </c>
       <c r="E4" s="10">
         <v>7.4</v>
       </c>
-      <c r="F4" s="1" t="s">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="26" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
+      <c r="D5" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="E5" s="10">
         <v>19.3</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="26" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="E6" s="10">
         <v>11.7</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="26" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E7" s="10">
         <v>20.8</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="26" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="E8" s="10">
         <v>24.8</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="26" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>33</v>
       </c>
       <c r="E9" s="11">
         <v>21.5</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>9</v>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/tables/table-1-partial-fine-tuning-architecture-specifications.xlsx
+++ b/tables/table-1-partial-fine-tuning-architecture-specifications.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0574198c81a0fd8/ERP/moth-classification-research-project/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="8_{BC1D83D8-9A1B-41C5-9595-46EA070E462D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FAFB4D2C-92C4-493B-9261-8456DB8CA34A}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="8_{BC1D83D8-9A1B-41C5-9595-46EA070E462D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0460E23D-5304-4425-B548-6A55855E04AA}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{02F10342-5E92-4A97-AD09-854D91C2ECB0}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{02F10342-5E92-4A97-AD09-854D91C2ECB0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -120,10 +120,10 @@
     <t>9.5M</t>
   </si>
   <si>
-    <t>Table 2: Partial Fine-Tuning Architecture Specifications</t>
-  </si>
-  <si>
     <t>Trainable Parameters (%)</t>
+  </si>
+  <si>
+    <t>Table 1: Partial Fine-Tuning Architecture Specifications</t>
   </si>
 </sst>
 </file>
@@ -275,9 +275,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -315,7 +315,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -421,7 +421,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -563,7 +563,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -572,25 +572,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BB5FD47-8783-4593-BDAE-5690A81077EC}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" customWidth="1"/>
-    <col min="3" max="3" width="18.85546875" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" customWidth="1"/>
+    <col min="1" max="1" width="15.453125" customWidth="1"/>
+    <col min="2" max="2" width="10.7265625" customWidth="1"/>
+    <col min="3" max="3" width="18.81640625" customWidth="1"/>
+    <col min="4" max="4" width="10.7265625" customWidth="1"/>
+    <col min="5" max="5" width="13.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
       <c r="D1" s="12"/>
       <c r="E1" s="12"/>
     </row>
-    <row r="2" spans="1:5" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
@@ -604,10 +604,10 @@
         <v>3</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -624,7 +624,7 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -641,7 +641,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
@@ -658,7 +658,7 @@
         <v>19.3</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
@@ -675,7 +675,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>20</v>
       </c>
@@ -686,13 +686,13 @@
         <v>22</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E7" s="10">
         <v>20.8</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>23</v>
       </c>
@@ -709,7 +709,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="26" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>27</v>
       </c>
